--- a/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,37</t>
+          <t>1,88; 8,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,79</t>
+          <t>-2,79; 3,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 18,64</t>
+          <t>10,49; 18,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,59</t>
+          <t>1,04; 6,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,48</t>
+          <t>0,6; 6,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 17,46</t>
+          <t>11,61; 17,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,43</t>
+          <t>2,27; 6,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,9</t>
+          <t>-0,24; 3,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 17,14</t>
+          <t>12,34; 17,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 86,07</t>
+          <t>16,63; 81,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 28,67</t>
+          <t>-22,97; 35,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,11; 185,34</t>
+          <t>82,81; 179,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 58,64</t>
+          <t>7,76; 58,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 59,16</t>
+          <t>3,24; 56,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,8; 162,07</t>
+          <t>86,19; 162,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 58,03</t>
+          <t>17,75; 60,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 36,76</t>
+          <t>-2,42; 36,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96,74; 158,59</t>
+          <t>96,44; 160,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,92</t>
+          <t>0,85; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,06</t>
+          <t>-0,15; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,49</t>
+          <t>2,84; 8,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,76</t>
+          <t>1,86; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,63</t>
+          <t>-0,67; 2,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 36,73</t>
+          <t>5,31; 39,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,43</t>
+          <t>1,92; 4,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,37</t>
+          <t>0,19; 2,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 24,47</t>
+          <t>5,29; 22,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 93,03</t>
+          <t>13,73; 99,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 76,98</t>
+          <t>-2,93; 74,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,32; 201,76</t>
+          <t>55,66; 195,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 129,39</t>
+          <t>27,34; 125,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 61,25</t>
+          <t>-11,08; 60,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,26; 823,54</t>
+          <t>94,66; 826,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,43; 96,17</t>
+          <t>33,71; 94,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 53,07</t>
+          <t>2,99; 53,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>104,02; 516,68</t>
+          <t>101,95; 481,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,1</t>
+          <t>-1,16; 4,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,81</t>
+          <t>-1,9; 3,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,63</t>
+          <t>2,45; 8,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,92</t>
+          <t>-1,28; 5,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,91</t>
+          <t>-3,99; 1,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,91</t>
+          <t>-0,95; 4,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,02</t>
+          <t>-0,37; 4,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,0</t>
+          <t>-2,07; 1,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,09</t>
+          <t>1,85; 5,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 166,59</t>
+          <t>-25,38; 174,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 111,54</t>
+          <t>-41,7; 137,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,19; 324,94</t>
+          <t>49,09; 354,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 141,65</t>
+          <t>-20,03; 139,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 45,39</t>
+          <t>-54,51; 48,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 117,85</t>
+          <t>-13,73; 124,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 115,51</t>
+          <t>-7,07; 115,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 56,21</t>
+          <t>-37,56; 46,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,6; 165,26</t>
+          <t>31,0; 162,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,18</t>
+          <t>1,49; 4,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,65</t>
+          <t>-1,04; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,81</t>
+          <t>3,24; 7,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,88</t>
+          <t>2,01; 4,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,03</t>
+          <t>-0,64; 2,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 23,49</t>
+          <t>5,54; 25,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,17</t>
+          <t>2,18; 4,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,48</t>
+          <t>-0,43; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 16,54</t>
+          <t>5,71; 17,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,97; 69,23</t>
+          <t>20,33; 71,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 27,0</t>
+          <t>-14,65; 24,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,6; 125,66</t>
+          <t>48,13; 128,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,83; 66,54</t>
+          <t>23,03; 66,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 27,16</t>
+          <t>-7,28; 27,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,22; 301,82</t>
+          <t>67,09; 313,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,44; 60,06</t>
+          <t>27,76; 59,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 21,47</t>
+          <t>-5,59; 20,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,64; 227,35</t>
+          <t>76,23; 242,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,65</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,05</t>
+          <t>2,03; 8,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,44</t>
+          <t>-2,8; 2,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 18,4</t>
+          <t>9,37; 16,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,42</t>
+          <t>1,09; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,39</t>
+          <t>0,36; 6,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 17,63</t>
+          <t>11,89; 18,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,46</t>
+          <t>2,22; 6,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,96</t>
+          <t>-0,16; 4,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,2</t>
+          <t>11,82; 16,42</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128,95%</t>
+          <t>116,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>120,54%</t>
+          <t>121,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>124,44%</t>
+          <t>119,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 81,98</t>
+          <t>16,15; 82,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 35,02</t>
+          <t>-22,77; 28,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,81; 179,91</t>
+          <t>74,49; 168,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 58,73</t>
+          <t>6,71; 59,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 56,15</t>
+          <t>1,99; 59,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,19; 162,31</t>
+          <t>86,94; 168,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 60,95</t>
+          <t>17,03; 57,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 36,95</t>
+          <t>-1,25; 37,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96,44; 160,38</t>
+          <t>92,86; 151,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,03</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,16</t>
+          <t>0,89; 4,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,05</t>
+          <t>-0,09; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,38</t>
+          <t>5,67; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,71</t>
+          <t>2,0; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,62</t>
+          <t>-0,46; 2,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 39,3</t>
+          <t>4,95; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,3</t>
+          <t>1,78; 4,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,41</t>
+          <t>0,12; 2,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 22,82</t>
+          <t>5,76; 8,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125,38%</t>
+          <t>149,15%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>263,03%</t>
+          <t>124,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>196,55%</t>
+          <t>136,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,73; 99,31</t>
+          <t>14,6; 98,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 74,57</t>
+          <t>-2,11; 69,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,66; 195,32</t>
+          <t>97,62; 219,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,34; 125,26</t>
+          <t>30,19; 121,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 60,55</t>
+          <t>-7,38; 61,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66; 826,16</t>
+          <t>78,3; 184,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,71; 94,04</t>
+          <t>31,95; 96,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 53,93</t>
+          <t>2,52; 52,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101,95; 481,15</t>
+          <t>101,0; 181,25</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,39</t>
+          <t>-1,48; 4,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,02</t>
+          <t>-2,19; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,74</t>
+          <t>2,62; 8,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,97</t>
+          <t>-1,23; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,87</t>
+          <t>-4,02; 2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,91</t>
+          <t>-1,04; 4,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,24</t>
+          <t>-0,47; 4,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,63</t>
+          <t>-2,29; 1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,89</t>
+          <t>1,81; 5,93</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148,5%</t>
+          <t>146,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 174,43</t>
+          <t>-29,92; 169,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 137,47</t>
+          <t>-46,34; 109,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,09; 354,45</t>
+          <t>44,16; 325,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 139,15</t>
+          <t>-17,62; 136,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 48,63</t>
+          <t>-53,56; 54,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 124,0</t>
+          <t>-13,75; 116,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 115,64</t>
+          <t>-9,68; 111,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 46,96</t>
+          <t>-38,21; 43,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,0; 162,64</t>
+          <t>31,63; 167,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>6,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,2</t>
+          <t>1,44; 4,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,54</t>
+          <t>-0,87; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,84</t>
+          <t>5,42; 8,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,88</t>
+          <t>1,93; 4,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,01</t>
+          <t>-0,65; 2,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 25,87</t>
+          <t>5,09; 7,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,16</t>
+          <t>2,14; 4,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,43</t>
+          <t>-0,3; 1,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 17,54</t>
+          <t>5,69; 7,72</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>103,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134,16%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116,5%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,33; 71,07</t>
+          <t>19,38; 72,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 24,92</t>
+          <t>-11,77; 28,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,13; 128,24</t>
+          <t>71,76; 137,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,03; 66,63</t>
+          <t>23,15; 67,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 27,45</t>
+          <t>-7,28; 29,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,09; 313,5</t>
+          <t>56,96; 106,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,76; 59,76</t>
+          <t>26,88; 59,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 20,16</t>
+          <t>-3,85; 22,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,23; 242,36</t>
+          <t>72,17; 113,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
